--- a/C255-10_SW_DFA报告_修改对照清单.xlsx
+++ b/C255-10_SW_DFA报告_修改对照清单.xlsx
@@ -12,9 +12,10 @@
     <sheet name="SW Arch对照" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Matrix对照" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="SafetyAnalysis对照" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="安全机制对照" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="General对照" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="核对清单" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="安全机制" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="安全机制对照" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="General对照" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="核对清单" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,6 +46,10 @@
       <b val="1"/>
       <color rgb="004472C4"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="5">
@@ -96,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -110,6 +115,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6752,6 +6763,260 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>SM ID</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>安全机制</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Traceability</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>诊断覆盖率</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>制动转向</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>RL_SM_01</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>电源监控器检测违反稳定电源的错误，以确保整个系统的供电，包括过压和欠压保护。此SM负责处理和诊断电源问题。</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>制动转向</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>RL_SM_02</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>对来电信号进行检测，判断转向灯、制动灯是否满足开启要求；当来电信号错误，功能灯不响应，转向灯、制动灯各自进入安全状态（转向反馈、制动由车身检查）。</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>制动转向</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>RL_SM_03</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>软件使用外部独立看门狗，当MCU软件故障可通过看门狗进行复位。</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>制动转向</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>RL_SM_04</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>灯具内部做故障判断逻辑，当判断故障后进行反馈，反馈机制应遵循奇瑞标准。</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>制动转向</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>RL_SM_05</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>当制动灯内部故障且故障无法反馈时，由车身进行电流检测以此判断制动灯故障状态。</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>制动转向</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>RL_SM_06</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>制动灯采用N-1&gt;=1方案进行设计，当某一组LED驱动或LED故障，剩余制动灯可以继续点亮。</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>制动转向</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>RL_SM_07</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>转向灯采用N-1=0方案进行设计，当某一组LED驱动或LED故障，剩余转向灯熄灭。</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>制动转向</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>RL_SM_08</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>在检测电路设计时，应考虑检测输出电压是否会导致MCU故障，故应使用钳位二极管将电压抑制在稳定区间。</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>制动转向</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>RL_SM_09</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>芯片硬件支持自检，并利用芯片特性设计外围电路。</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>制动转向</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6937,7 +7202,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7235,7 +7500,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
